--- a/data/ams_weekly_data/Nexlev/ads_report_week32.xlsx
+++ b/data/ams_weekly_data/Nexlev/ads_report_week32.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,42 +419,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -938,7 +927,7 @@
         <v>1961</v>
       </c>
       <c r="F18" t="n">
-        <v>287421</v>
+        <v>287419</v>
       </c>
       <c r="G18" t="n">
         <v>123198.28</v>
@@ -1168,7 +1157,7 @@
         <v>60231.35</v>
       </c>
       <c r="H26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27">
@@ -1246,7 +1235,7 @@
         <v>48</v>
       </c>
       <c r="F29" t="n">
-        <v>7766</v>
+        <v>7765</v>
       </c>
       <c r="G29" t="n">
         <v>4103.389999999999</v>
@@ -1473,10 +1462,10 @@
         <v>9035</v>
       </c>
       <c r="G37" t="n">
-        <v>9879.66</v>
+        <v>14772.03</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -1694,7 +1683,7 @@
         <v>196</v>
       </c>
       <c r="F45" t="n">
-        <v>78131</v>
+        <v>78130</v>
       </c>
       <c r="G45" t="n">
         <v>1863.56</v>
@@ -2142,13 +2131,13 @@
         <v>305</v>
       </c>
       <c r="F61" t="n">
-        <v>59079</v>
+        <v>59077</v>
       </c>
       <c r="G61" t="n">
-        <v>51227.95</v>
+        <v>56023.71</v>
       </c>
       <c r="H61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
@@ -2229,10 +2218,10 @@
         <v>138396</v>
       </c>
       <c r="G64" t="n">
-        <v>13425.43</v>
+        <v>14992.38</v>
       </c>
       <c r="H64" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -2344,7 +2333,7 @@
         <v>23335.61</v>
       </c>
       <c r="H68" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -2444,13 +2433,13 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>24558.51</v>
+        <v>24541.76</v>
       </c>
       <c r="E72" t="n">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F72" t="n">
-        <v>95082</v>
+        <v>95081</v>
       </c>
       <c r="G72" t="n">
         <v>61898.28</v>
@@ -2565,10 +2554,10 @@
         <v>54695</v>
       </c>
       <c r="G76" t="n">
-        <v>1863.56</v>
+        <v>3727.12</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -2590,7 +2579,7 @@
         <v>68</v>
       </c>
       <c r="F77" t="n">
-        <v>20562</v>
+        <v>20561</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2677,10 +2666,10 @@
         <v>50690</v>
       </c>
       <c r="G80" t="n">
-        <v>80399.13</v>
+        <v>89915.23000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81">
@@ -2733,10 +2722,10 @@
         <v>26683</v>
       </c>
       <c r="G82" t="n">
-        <v>52376.25999999999</v>
+        <v>61892.36</v>
       </c>
       <c r="H82" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83">
@@ -2792,7 +2781,7 @@
         <v>12870.34</v>
       </c>
       <c r="H84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -3430,7 +3419,7 @@
         <v>276</v>
       </c>
       <c r="F107" t="n">
-        <v>51802</v>
+        <v>51801</v>
       </c>
       <c r="G107" t="n">
         <v>61727.1</v>
@@ -3822,7 +3811,7 @@
         <v>39</v>
       </c>
       <c r="F121" t="n">
-        <v>20314</v>
+        <v>20313</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -4077,10 +4066,10 @@
         <v>136558</v>
       </c>
       <c r="G130" t="n">
-        <v>38716.94</v>
+        <v>48377.11</v>
       </c>
       <c r="H130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
@@ -7266,13 +7255,13 @@
         <v>211</v>
       </c>
       <c r="F244" t="n">
-        <v>11104</v>
+        <v>11102</v>
       </c>
       <c r="G244" t="n">
-        <v>87746.59</v>
+        <v>97262.69</v>
       </c>
       <c r="H244" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="245">
@@ -8022,7 +8011,7 @@
         <v>174</v>
       </c>
       <c r="F271" t="n">
-        <v>16832</v>
+        <v>16831</v>
       </c>
       <c r="G271" t="n">
         <v>4490.68</v>
@@ -8389,10 +8378,10 @@
         <v>3196</v>
       </c>
       <c r="G284" t="n">
-        <v>3456.78</v>
+        <v>6845.76</v>
       </c>
       <c r="H284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="285">
@@ -8582,13 +8571,13 @@
         <v>446</v>
       </c>
       <c r="F291" t="n">
-        <v>47701</v>
+        <v>47700</v>
       </c>
       <c r="G291" t="n">
-        <v>12112.73</v>
+        <v>13806.8</v>
       </c>
       <c r="H291" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="292">
@@ -8632,13 +8621,13 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>5052.82</v>
+        <v>5044.82</v>
       </c>
       <c r="E293" t="n">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="F293" t="n">
-        <v>45248</v>
+        <v>45247</v>
       </c>
       <c r="G293" t="n">
         <v>14021.18</v>
@@ -8837,10 +8826,10 @@
         <v>42054</v>
       </c>
       <c r="G300" t="n">
-        <v>38064.4</v>
+        <v>47580.5</v>
       </c>
       <c r="H300" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8858,42 +8847,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Portfolio name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Campaign Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Advertised ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Spend</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Clicks</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Impressions</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>14 Day Total Sales (₹)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>14 Day Total Units (#)</t>
         </is>
@@ -8912,10 +8901,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1046.22</v>
+        <v>1032.58</v>
       </c>
       <c r="E2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F2" t="n">
         <v>38413</v>
@@ -10241,6 +10230,1816 @@
       </c>
       <c r="H49" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3239</v>
+      </c>
+      <c r="E2" t="n">
+        <v>111</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1782.251616551025</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5151.265414002617</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Nexlev - B0DCK7ZH5P - Carpet &amp; Car Seat Vacuum Cleaner - SBV- BM</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3877</v>
+      </c>
+      <c r="E3" t="n">
+        <v>133</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2133.808383448975</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6167.374585997381</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0D67727VG</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10262</v>
+      </c>
+      <c r="E4" t="n">
+        <v>37</v>
+      </c>
+      <c r="F4" t="n">
+        <v>674.1668219583444</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1046.67</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Nexlev -Catch All- Scalp Massager-SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0DKK15YNJ</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>23333</v>
+      </c>
+      <c r="E5" t="n">
+        <v>83</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1532.973178041656</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2380</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- BM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>18046</v>
+      </c>
+      <c r="E6" t="n">
+        <v>419</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4194.27</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13555.92</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- Exact</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5546</v>
+      </c>
+      <c r="E7" t="n">
+        <v>203</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1770.415219317728</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13555.92</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CDPP45BM-Steam Cleaner-SBV- Exact</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2163</v>
+      </c>
+      <c r="E8" t="n">
+        <v>79</v>
+      </c>
+      <c r="F8" t="n">
+        <v>690.5247806822723</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5287.29</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7664</v>
+      </c>
+      <c r="E9" t="n">
+        <v>281</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3709.896814318231</v>
+      </c>
+      <c r="G9" t="n">
+        <v>22631.38146375582</v>
+      </c>
+      <c r="H9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner - SBV-Phrase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2222</v>
+      </c>
+      <c r="E10" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1075.663185681768</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6561.838536244185</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Nexlev-B0CYSLCRQS-Vacuum Cleaner -SB-KT-Phrase(Video)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13372</v>
+      </c>
+      <c r="E11" t="n">
+        <v>286</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2126.49</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-SBV-Phrase-Mop Cleaner</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>17333</v>
+      </c>
+      <c r="E12" t="n">
+        <v>148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2648.46</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4795.76</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SBV- Exact</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5635</v>
+      </c>
+      <c r="E13" t="n">
+        <v>73</v>
+      </c>
+      <c r="F13" t="n">
+        <v>718.54</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5083.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Nexlev-B0DNJS23HS-Steam Cleaner-SBV- PT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>19319</v>
+      </c>
+      <c r="E14" t="n">
+        <v>183</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2398.14</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-Exact- SBV</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11310</v>
+      </c>
+      <c r="E15" t="n">
+        <v>32</v>
+      </c>
+      <c r="F15" t="n">
+        <v>783.0999999999999</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Nexlev-B0GGHZWMVW-Vacuum-PT01-SBV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8951</v>
+      </c>
+      <c r="E16" t="n">
+        <v>157</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2511.71</v>
+      </c>
+      <c r="G16" t="n">
+        <v>10168.64</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5787</v>
+      </c>
+      <c r="E17" t="n">
+        <v>79</v>
+      </c>
+      <c r="F17" t="n">
+        <v>762.4362060824437</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10728.45430116921</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11411</v>
+      </c>
+      <c r="E18" t="n">
+        <v>156</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1503.393286867981</v>
+      </c>
+      <c r="G18" t="n">
+        <v>21154.6697889943</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6896</v>
+      </c>
+      <c r="E19" t="n">
+        <v>94</v>
+      </c>
+      <c r="F19" t="n">
+        <v>908.5433026791076</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12784.36835195647</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Nexlev-Catch All-Steam Cleaner -SB-KT-Exact/Phrase</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10833</v>
+      </c>
+      <c r="E20" t="n">
+        <v>148</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1427.257204370468</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20083.33755788002</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Nexlev-Foldable Steam Cleaner-B0DNJS23HS-SBV-PT2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4342</v>
+      </c>
+      <c r="E21" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" t="n">
+        <v>471.91</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Nexlev-Spot Cleaner Machine-B0GGHZWMVW-SBV-PT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2382</v>
+      </c>
+      <c r="E22" t="n">
+        <v>19</v>
+      </c>
+      <c r="F22" t="n">
+        <v>173.92</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Nexlev-Spot Cleaner Machine-B0GGHZWMVW-SBV-PT2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2809</v>
+      </c>
+      <c r="E23" t="n">
+        <v>53</v>
+      </c>
+      <c r="F23" t="n">
+        <v>567.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Nexlev-Steam Cleaner-B0CDPP45BM-SBV-BM</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E24" t="n">
+        <v>28</v>
+      </c>
+      <c r="F24" t="n">
+        <v>132.02</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Nexlev-Steam Cleaner-B0CDPP45BM-SBV-BM2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>506</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16</v>
+      </c>
+      <c r="F25" t="n">
+        <v>111.26</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>18381</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1157</v>
+      </c>
+      <c r="F26" t="n">
+        <v>10874.49052793781</v>
+      </c>
+      <c r="G26" t="n">
+        <v>126199.9802133671</v>
+      </c>
+      <c r="H26" t="n">
+        <v>39</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>421</v>
+      </c>
+      <c r="E27" t="n">
+        <v>26</v>
+      </c>
+      <c r="F27" t="n">
+        <v>248.8758912459931</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2888.239450863226</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>9341</v>
+      </c>
+      <c r="E28" t="n">
+        <v>588</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5526.532492365246</v>
+      </c>
+      <c r="G28" t="n">
+        <v>64136.18085308919</v>
+      </c>
+      <c r="H28" t="n">
+        <v>20</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>B0F2N1HTBT</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>44</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>26.21123639110792</v>
+      </c>
+      <c r="G29" t="n">
+        <v>304.1850563414851</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Nexlev-Steamer-PT(SEAHELTON)-SB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>17939</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10612.99985205984</v>
+      </c>
+      <c r="G30" t="n">
+        <v>123165.344426339</v>
+      </c>
+      <c r="H30" t="n">
+        <v>38</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10681</v>
+      </c>
+      <c r="E31" t="n">
+        <v>208</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1717.08</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3388.98</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>22828</v>
+      </c>
+      <c r="E32" t="n">
+        <v>422</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3756.716231221539</v>
+      </c>
+      <c r="G32" t="n">
+        <v>11493.11463195395</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CDPP45BM_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>9987</v>
+      </c>
+      <c r="E33" t="n">
+        <v>185</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1643.503768778462</v>
+      </c>
+      <c r="G33" t="n">
+        <v>5028.055368046054</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E34" t="n">
+        <v>45</v>
+      </c>
+      <c r="F34" t="n">
+        <v>428.29</v>
+      </c>
+      <c r="G34" t="n">
+        <v>7353.4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Nexlev_B0CYSLCRQS_Sofa Cleaning Machine_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B0CYSLCRQS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>30019</v>
+      </c>
+      <c r="E35" t="n">
+        <v>389</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4357.23</v>
+      </c>
+      <c r="G35" t="n">
+        <v>12639.83</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_KT_Phrase</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>649</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" t="n">
+        <v>86.16</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2778.81</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Nexlev_B0DCK7ZH5P_Sofa Cleaning Machine_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11297</v>
+      </c>
+      <c r="E37" t="n">
+        <v>257</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2594.85</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2880.51</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_KT_BM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>14702</v>
+      </c>
+      <c r="E38" t="n">
+        <v>461</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4754.12</v>
+      </c>
+      <c r="G38" t="n">
+        <v>42717.77</v>
+      </c>
+      <c r="H38" t="n">
+        <v>15</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>23778</v>
+      </c>
+      <c r="E39" t="n">
+        <v>430</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3823.178510122336</v>
+      </c>
+      <c r="G39" t="n">
+        <v>35222.84701789803</v>
+      </c>
+      <c r="H39" t="n">
+        <v>11</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Nexlev_B0F43P6D23_Steam Cleaner_SBV_PT</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7336</v>
+      </c>
+      <c r="E40" t="n">
+        <v>133</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1179.621489877664</v>
+      </c>
+      <c r="G40" t="n">
+        <v>10867.82298210197</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - BM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>256</v>
+      </c>
+      <c r="E41" t="n">
+        <v>7</v>
+      </c>
+      <c r="F41" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B08126296H</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>630</v>
+      </c>
+      <c r="E42" t="n">
+        <v>21</v>
+      </c>
+      <c r="F42" t="n">
+        <v>185.7886181586628</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3857.314300655654</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0CDPP45BM</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>774</v>
+      </c>
+      <c r="E43" t="n">
+        <v>25</v>
+      </c>
+      <c r="F43" t="n">
+        <v>228.0497333046036</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4734.732979096326</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - PT</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1393</v>
+      </c>
+      <c r="E44" t="n">
+        <v>45</v>
+      </c>
+      <c r="F44" t="n">
+        <v>410.4784841333032</v>
+      </c>
+      <c r="G44" t="n">
+        <v>8522.29023850468</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - PT</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>B0GGHZWMVW</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2172</v>
+      </c>
+      <c r="E45" t="n">
+        <v>71</v>
+      </c>
+      <c r="F45" t="n">
+        <v>640.3531644034306</v>
+      </c>
+      <c r="G45" t="n">
+        <v>13294.91248174334</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - Phrase</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3716</v>
+      </c>
+      <c r="E46" t="n">
+        <v>45</v>
+      </c>
+      <c r="F46" t="n">
+        <v>641.47</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - Phrase - SB</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4450</v>
+      </c>
+      <c r="E47" t="n">
+        <v>43</v>
+      </c>
+      <c r="F47" t="n">
+        <v>609.6900000000001</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - BM</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>292</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>103.66</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - KT</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E49" t="n">
+        <v>46</v>
+      </c>
+      <c r="F49" t="n">
+        <v>652.9400000000001</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaner - SB - PT</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1131</v>
+      </c>
+      <c r="E50" t="n">
+        <v>32</v>
+      </c>
+      <c r="F50" t="n">
+        <v>279.23</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Nexlex - Steam Cleaning - SB - Phrase</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>B0F43P6D23</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>3938</v>
+      </c>
+      <c r="E51" t="n">
+        <v>49</v>
+      </c>
+      <c r="F51" t="n">
+        <v>632.11</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Nexliv-B0DNJS23HS-BM-SBV</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>B0DNJS23HS</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1829</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" t="n">
+        <v>430.61</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase -</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>16133</v>
+      </c>
+      <c r="E53" t="n">
+        <v>144</v>
+      </c>
+      <c r="F53" t="n">
+        <v>966.74</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nexllev-Vacuum Cleaner-B0DCK7ZH5P-SBV- phrase-01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>B0DCK7ZH5P</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3939</v>
+      </c>
+      <c r="E54" t="n">
+        <v>78</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1195.79</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Nexlev</t>
+        </is>
       </c>
     </row>
   </sheetData>
